--- a/data/nzd0245/nzd0245.xlsx
+++ b/data/nzd0245/nzd0245.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M343"/>
+  <dimension ref="A1:M344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15830,13 +15830,13 @@
         <v>367.5</v>
       </c>
       <c r="F343" t="n">
-        <v>360.46</v>
+        <v>363.51</v>
       </c>
       <c r="G343" t="n">
         <v>359.96</v>
       </c>
       <c r="H343" t="n">
-        <v>360.99</v>
+        <v>364.4</v>
       </c>
       <c r="I343" t="n">
         <v>372.92</v>
@@ -15848,9 +15848,54 @@
         <v>389.61</v>
       </c>
       <c r="L343" t="n">
-        <v>368.14</v>
+        <v>369.66</v>
       </c>
       <c r="M343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>397.69</v>
+      </c>
+      <c r="C344" t="n">
+        <v>357.72</v>
+      </c>
+      <c r="D344" t="n">
+        <v>356.76</v>
+      </c>
+      <c r="E344" t="n">
+        <v>367.08</v>
+      </c>
+      <c r="F344" t="n">
+        <v>362.87</v>
+      </c>
+      <c r="G344" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="H344" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="I344" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="J344" t="n">
+        <v>378.87</v>
+      </c>
+      <c r="K344" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="L344" t="n">
+        <v>365.26</v>
+      </c>
+      <c r="M344" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15867,7 +15912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19500,6 +19545,16 @@
       </c>
       <c r="B363" t="n">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -19668,28 +19723,28 @@
         <v>0.0255</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3359411342811278</v>
+        <v>0.3409094080858838</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0365078381891295</v>
+        <v>0.03773511621092096</v>
       </c>
       <c r="M2" t="n">
-        <v>10.84015822959268</v>
+        <v>10.83134440468632</v>
       </c>
       <c r="N2" t="n">
-        <v>175.4278660892397</v>
+        <v>175.1428452799597</v>
       </c>
       <c r="O2" t="n">
-        <v>13.24491850066431</v>
+        <v>13.23415449811433</v>
       </c>
       <c r="P2" t="n">
-        <v>379.7838620445822</v>
+        <v>379.7326722506394</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19746,28 +19801,28 @@
         <v>0.046</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4306886891664277</v>
+        <v>0.4302907123095799</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07296595588460109</v>
+        <v>0.07326826946049614</v>
       </c>
       <c r="M3" t="n">
-        <v>9.266902706575499</v>
+        <v>9.242027608140202</v>
       </c>
       <c r="N3" t="n">
-        <v>138.0141931033213</v>
+        <v>137.613287254032</v>
       </c>
       <c r="O3" t="n">
-        <v>11.74794420753356</v>
+        <v>11.73086898972246</v>
       </c>
       <c r="P3" t="n">
-        <v>346.8942723972086</v>
+        <v>346.8983765225846</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19824,28 +19879,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3369186291156906</v>
+        <v>0.3373053901192565</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05402538540310253</v>
+        <v>0.05446674872793056</v>
       </c>
       <c r="M4" t="n">
-        <v>8.507782595493888</v>
+        <v>8.485034381698872</v>
       </c>
       <c r="N4" t="n">
-        <v>116.4000238193083</v>
+        <v>116.0620514699175</v>
       </c>
       <c r="O4" t="n">
-        <v>10.78888427129091</v>
+        <v>10.77320989630841</v>
       </c>
       <c r="P4" t="n">
-        <v>347.0471520717768</v>
+        <v>347.043163609579</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19902,28 +19957,28 @@
         <v>0.0306</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2784498360502818</v>
+        <v>0.2829990692575072</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03140189246415859</v>
+        <v>0.03255891913875453</v>
       </c>
       <c r="M5" t="n">
-        <v>9.498292221651685</v>
+        <v>9.493343914508216</v>
       </c>
       <c r="N5" t="n">
-        <v>139.5533318391952</v>
+        <v>139.3335158835551</v>
       </c>
       <c r="O5" t="n">
-        <v>11.81326931205732</v>
+        <v>11.80396187233571</v>
       </c>
       <c r="P5" t="n">
-        <v>351.5308452368201</v>
+        <v>351.4837100036011</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19980,28 +20035,28 @@
         <v>0.0319</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2350402416634758</v>
+        <v>0.2373252788561478</v>
       </c>
       <c r="J6" t="n">
+        <v>343</v>
+      </c>
+      <c r="K6" t="n">
         <v>342</v>
       </c>
-      <c r="K6" t="n">
-        <v>341</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02081743042052475</v>
+        <v>0.0213468533596245</v>
       </c>
       <c r="M6" t="n">
-        <v>9.612785708032975</v>
+        <v>9.590792085714416</v>
       </c>
       <c r="N6" t="n">
-        <v>150.7844173127467</v>
+        <v>150.3497212974029</v>
       </c>
       <c r="O6" t="n">
-        <v>12.27943065914486</v>
+        <v>12.26171771398294</v>
       </c>
       <c r="P6" t="n">
-        <v>355.5306690000902</v>
+        <v>355.5070444815905</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20058,28 +20113,28 @@
         <v>0.0426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2830092320258828</v>
+        <v>0.2859404132441775</v>
       </c>
       <c r="J7" t="n">
+        <v>343</v>
+      </c>
+      <c r="K7" t="n">
         <v>342</v>
       </c>
-      <c r="K7" t="n">
-        <v>341</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.04674419201674707</v>
+        <v>0.04792039807285475</v>
       </c>
       <c r="M7" t="n">
-        <v>7.750945386100345</v>
+        <v>7.746715912722641</v>
       </c>
       <c r="N7" t="n">
-        <v>95.89356623249317</v>
+        <v>95.69308924964589</v>
       </c>
       <c r="O7" t="n">
-        <v>9.792526039408482</v>
+        <v>9.782284459656951</v>
       </c>
       <c r="P7" t="n">
-        <v>350.6885956697992</v>
+        <v>350.6583924294226</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20136,28 +20191,28 @@
         <v>0.0378</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08176975504152084</v>
+        <v>0.08579792119298361</v>
       </c>
       <c r="J8" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K8" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004254024258358857</v>
+        <v>0.004705800081077682</v>
       </c>
       <c r="M8" t="n">
-        <v>7.675136337029397</v>
+        <v>7.674516093107767</v>
       </c>
       <c r="N8" t="n">
-        <v>92.10720496190868</v>
+        <v>91.93786395480976</v>
       </c>
       <c r="O8" t="n">
-        <v>9.597249864513723</v>
+        <v>9.588423434267479</v>
       </c>
       <c r="P8" t="n">
-        <v>357.5770240175165</v>
+        <v>357.535665044269</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20214,28 +20269,28 @@
         <v>0.0317</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.226351550799771</v>
+        <v>-0.2192457198365458</v>
       </c>
       <c r="J9" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K9" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02023855690740795</v>
+        <v>0.01906938724807938</v>
       </c>
       <c r="M9" t="n">
-        <v>9.776406330840619</v>
+        <v>9.782205435559796</v>
       </c>
       <c r="N9" t="n">
-        <v>145.2543548293256</v>
+        <v>145.2988320373145</v>
       </c>
       <c r="O9" t="n">
-        <v>12.05215146060344</v>
+        <v>12.05399651722674</v>
       </c>
       <c r="P9" t="n">
-        <v>368.5953850174558</v>
+        <v>368.5221063313428</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20292,28 +20347,28 @@
         <v>0.0313</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04153902890195475</v>
+        <v>0.04934979403860224</v>
       </c>
       <c r="J10" t="n">
+        <v>343</v>
+      </c>
+      <c r="K10" t="n">
         <v>342</v>
       </c>
-      <c r="K10" t="n">
-        <v>341</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0006003750632230798</v>
+        <v>0.000849713375205785</v>
       </c>
       <c r="M10" t="n">
-        <v>9.5124834309135</v>
+        <v>9.528630128590002</v>
       </c>
       <c r="N10" t="n">
-        <v>166.6727785226929</v>
+        <v>166.7434371077758</v>
       </c>
       <c r="O10" t="n">
-        <v>12.91018119635402</v>
+        <v>12.91291745144279</v>
       </c>
       <c r="P10" t="n">
-        <v>363.8803350209457</v>
+        <v>363.7992237789066</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20370,28 +20425,28 @@
         <v>0.0273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1709321471815009</v>
+        <v>-0.1605540535136767</v>
       </c>
       <c r="J11" t="n">
+        <v>343</v>
+      </c>
+      <c r="K11" t="n">
         <v>342</v>
       </c>
-      <c r="K11" t="n">
-        <v>341</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01195933027676488</v>
+        <v>0.01055894239316979</v>
       </c>
       <c r="M11" t="n">
-        <v>9.266544971579169</v>
+        <v>9.292502561958162</v>
       </c>
       <c r="N11" t="n">
-        <v>140.0718670897962</v>
+        <v>140.6474149223318</v>
       </c>
       <c r="O11" t="n">
-        <v>11.83519611539227</v>
+        <v>11.85948628408212</v>
       </c>
       <c r="P11" t="n">
-        <v>372.5363836843092</v>
+        <v>372.4286119036105</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -20448,28 +20503,28 @@
         <v>0.0316</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1969273550492194</v>
+        <v>0.19689713177498</v>
       </c>
       <c r="J12" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K12" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01149844270335565</v>
+        <v>0.01156572777744114</v>
       </c>
       <c r="M12" t="n">
-        <v>10.96904990673607</v>
+        <v>10.94574323707097</v>
       </c>
       <c r="N12" t="n">
-        <v>192.8159658911778</v>
+        <v>192.2732467729717</v>
       </c>
       <c r="O12" t="n">
-        <v>13.88581887722787</v>
+        <v>13.8662628985957</v>
       </c>
       <c r="P12" t="n">
-        <v>361.5416648562486</v>
+        <v>361.5420332364058</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -20507,7 +20562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M343"/>
+  <dimension ref="A1:M344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43388,7 +43443,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>-38.09979992024755,174.76393921386668</t>
+          <t>-38.09978860699017,174.76390752145346</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -43398,7 +43453,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>-38.09851716758904,174.7646946070573</t>
+          <t>-38.09850451913385,174.76465917445097</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -43418,10 +43473,77 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>-38.09592900636278,174.76614211598798</t>
+          <t>-38.09592336845737,174.76612632248003</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-38.10222332685905,174.76203054665737</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-38.101731221856724,174.76282633528228</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-38.10109440898787,174.76321676069497</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-38.100415749735,174.7634899750669</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-38.09979098092032,174.76391417166397</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-38.09914817938115,174.76428786794625</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-38.098507449422094,174.76466738317689</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-38.09782383538312,174.76492678185693</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-38.09717003806916,174.7652697230707</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-38.09650169527921,174.7655719339993</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-38.09593968870384,174.76617204053582</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
